--- a/templates/poam-tracker.xlsx
+++ b/templates/poam-tracker.xlsx
@@ -902,5 +902,13 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;LField Notes Lab  -  fictional, for teaching&amp;COmar Mahdy&amp;R&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/templates/poam-tracker.xlsx
+++ b/templates/poam-tracker.xlsx
@@ -524,7 +524,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>The master list of known weaknesses and how they get fixed. This is the working heart of a security programme.</t>
+          <t>The organisation-wide master list of known weaknesses and how they get fixed. A weakness found while assessing one system is tracked here against the system where it matters most, so items assessed on the portal may land on another system.</t>
         </is>
       </c>
     </row>
